--- a/data/trans_dic/P32E$eventos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,66</t>
+          <t>0,0; 35,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,88</t>
+          <t>0,0; 81,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 37,97</t>
+          <t>4,0; 38,97</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,24</t>
+          <t>0,0; 31,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,61</t>
+          <t>0,0; 52,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 31,89</t>
+          <t>3,36; 31,48</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,47</t>
+          <t>0,0; 39,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,79</t>
+          <t>0,0; 11,52</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,09</t>
+          <t>0,6; 5,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 23,55</t>
+          <t>2,43; 22,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,13</t>
+          <t>1,8; 8,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6462</t>
+          <t>0; 6846</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5099</t>
+          <t>0; 5100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1032; 9654</t>
+          <t>1017; 9908</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3580</t>
+          <t>0; 4274</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6000</t>
+          <t>0; 6144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>840; 8058</t>
+          <t>849; 7955</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2066</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 672</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1877</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1719</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4083</t>
+          <t>0; 4240</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4826</t>
+          <t>0; 5677</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1856</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1173</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1711</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2406</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2262</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2524</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>877; 8555</t>
+          <t>848; 7287</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1213; 11968</t>
+          <t>1236; 11411</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3163; 15550</t>
+          <t>3440; 15686</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$eventos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,66</t>
+          <t>0,0; 33,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,9</t>
+          <t>0,0; 78,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 38,97</t>
+          <t>3,56; 33,37</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,33</t>
+          <t>0,0; 35,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,85</t>
+          <t>0,0; 48,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 31,48</t>
+          <t>3,61; 30,22</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,94</t>
+          <t>0,0; 26,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,52</t>
+          <t>0,0; 8,26</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,19</t>
+          <t>0,57; 5,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 22,45</t>
+          <t>1,92; 19,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,2</t>
+          <t>1,66; 7,19</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3744</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6846</t>
+          <t>0; 6818</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5100</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1017; 9908</t>
+          <t>958; 8981</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3469</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4274</t>
+          <t>0; 5372</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6144</t>
+          <t>0; 6462</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>849; 7955</t>
+          <t>1036; 8675</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4240</t>
+          <t>0; 3943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5677</t>
+          <t>0; 4682</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>848; 7287</t>
+          <t>906; 8138</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1236; 11411</t>
+          <t>1157; 11917</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3440; 15686</t>
+          <t>3617; 15667</t>
         </is>
       </c>
     </row>
